--- a/PO_Items.xlsx
+++ b/PO_Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Desktop\Meen\OCR\Tracking\Trackinggggg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2BBF24-93F4-4954-AB22-A0C2454DB610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8924EC6-D7FE-45E9-8076-68539EE1FE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4365,7 +4365,8 @@
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
